--- a/reports/pdf_weekly_20260904.xlsx
+++ b/reports/pdf_weekly_20260904.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,425억   ·   현금 48억(1.1%)      주말 2026-09-04  vs  주초 2026-08-31      매수 9종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,314억   ·   현금 24억(0.5%)      주말 2026-09-04  vs  주초 2026-08-31      매수 9종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>109</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1310207250</v>
+        <v>1306365000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-98</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-6446332200</v>
+        <v>-6427428000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1617669900</v>
+        <v>1612926000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-72</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-5067532800</v>
+        <v>-5052672000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2423793900</v>
+        <v>2416686000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-18</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1058805000</v>
+        <v>-1055700000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>3311962500</v>
+        <v>3302250000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-12</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-583110000</v>
+        <v>-581400000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1588514400</v>
+        <v>1583856000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-10</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1012770000</v>
+        <v>-1009800000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>769398300</v>
+        <v>767142000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-9</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2605581000</v>
+        <v>-2597940000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>854409600</v>
+        <v>851904000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5558982000</v>
+        <v>5542680000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>878245500</v>
+        <v>875670000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,652억   ·   현금 24억(0.7%)      주말 2026-09-04  vs  주초 2026-08-31      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,530억   ·   현금 12억(0.3%)      주말 2026-09-04  vs  주초 2026-08-31      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1035,7 +1035,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,471억   ·   현금 62억(2.6%)      주말 2026-09-04  vs  주초 2026-08-31      매수 7종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,410억   ·   현금 31억(1.3%)      주말 2026-09-04  vs  주초 2026-08-31      매수 7종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1131,7 +1131,7 @@
         <v>333</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>2327403600</v>
+        <v>2330766900</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>-92</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1298745600</v>
+        <v>-1300622400</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>300</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1833108000</v>
+        <v>1835757000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>-71</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1149688800</v>
+        <v>-1151350200</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>97</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>3369624800</v>
+        <v>3374494200</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>-40</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1790896000</v>
+        <v>-1793484000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>19</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1206986400</v>
+        <v>1208730600</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>-32</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-735180800</v>
+        <v>-736243200</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>470836800</v>
+        <v>471517200</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>-29</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-2004793200</v>
+        <v>-2007690300</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>2314048000</v>
+        <v>2317392000</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>-15</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1219650000</v>
+        <v>-1221412500</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>294792000</v>
+        <v>295218000</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1409,23 +1409,23 @@
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>로보티즈  (편출)</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1204564400</v>
+        <v>-2180178000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>4.59%→4.13%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>119→106</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -1437,30 +1437,30 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>로보티즈  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-2177032000</v>
+        <v>-1206305100</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>4.59%→4.13%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>119→106</t>
         </is>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,065억   ·   현금 50억(2.5%)      주말 2026-09-04  vs  주초 2026-08-31      매수 2종목  /  매도 7종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,990억   ·   현금 25억(1.2%)      주말 2026-09-04  vs  주초 2026-08-31      매수 2종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1556,7 +1556,7 @@
         <v>52</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>2587187200</v>
+        <v>2556569600</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>-122</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1999946000</v>
+        <v>-1976278000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>18</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1138316400</v>
+        <v>1124845200</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>-119</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-325395980</v>
+        <v>-321545140</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>-80</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-605696000</v>
+        <v>-598528000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>-45</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-414472500</v>
+        <v>-409567500</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>-44</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-303388800</v>
+        <v>-299798400</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>-17</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-145086500</v>
+        <v>-143369500</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>-5</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-26735800</v>
+        <v>-26419400</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 262억   ·   현금 3억(1.0%)      주말 2026-09-04  vs  주초 2026-08-31      매수 11종목  /  매도 9종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 257억   ·   현금 1억(0.5%)      주말 2026-09-04  vs  주초 2026-08-31      매수 11종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B42" s="4" t="n"/>
@@ -1873,11 +1873,11 @@
         <v>89</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>120301300</v>
+        <v>115753400</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.05%→2.50%</t>
+          <t>2.01%→2.45%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1894,11 +1894,11 @@
         <v>-386</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-281008000</v>
+        <v>-272902000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>8.67%→7.56%</t>
+          <t>8.58%→7.49%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -1917,11 +1917,11 @@
         <v>47</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>51817500</v>
+        <v>51126600</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>3.30%→3.49%</t>
+          <t>3.32%→3.51%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -1938,11 +1938,11 @@
         <v>-52</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-36254400</v>
+        <v>-35271600</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.92%</t>
+          <t>1.06%→0.92%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -1961,11 +1961,11 @@
         <v>41</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>97006000</v>
+        <v>98728000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>3.03%→3.40%</t>
+          <t>3.15%→3.53%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -1982,11 +1982,11 @@
         <v>-32</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-46480000</v>
+        <v>-46368000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>5.55%→5.36%</t>
+          <t>5.65%→5.45%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2005,11 +2005,11 @@
         <v>33</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>77154000</v>
+        <v>76692000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>6.70%→6.97%</t>
+          <t>6.79%→7.07%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2026,11 +2026,11 @@
         <v>-31</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-85932000</v>
+        <v>-86149000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>3.06%→2.72%</t>
+          <t>3.13%→2.79%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2049,11 +2049,11 @@
         <v>30</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>55335000</v>
+        <v>51030000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>2.35%→2.56%</t>
+          <t>2.21%→2.40%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2070,11 +2070,11 @@
         <v>-31</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-26864600</v>
+        <v>-26604200</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2.67%→2.55%</t>
+          <t>2.69%→2.58%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2093,11 +2093,11 @@
         <v>29</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>101703000</v>
+        <v>100586500</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>0.78%→1.17%</t>
+          <t>0.79%→1.18%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2114,7 +2114,7 @@
         <v>-15</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-33915000</v>
+        <v>-33285000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2137,11 +2137,11 @@
         <v>21</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>82026000</v>
+        <v>76293000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>2.89%→3.19%</t>
+          <t>2.74%→3.03%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2158,11 +2158,11 @@
         <v>-13</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-53599000</v>
+        <v>-51597000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>1.92%→1.71%</t>
+          <t>1.89%→1.68%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2181,11 +2181,11 @@
         <v>15</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>35385000</v>
+        <v>34387500</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.09%→1.22%</t>
+          <t>1.08%→1.21%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2202,11 +2202,11 @@
         <v>-10</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-35280000</v>
+        <v>-35140000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.43%→1.29%</t>
+          <t>1.45%→1.31%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2225,7 +2225,7 @@
         <v>14</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>68208000</v>
+        <v>67228000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2246,11 +2246,11 @@
         <v>-3</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-82425000</v>
+        <v>-80010000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.32%→0.00%</t>
+          <t>0.31%→0.00%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2269,11 +2269,11 @@
         <v>11</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>24486000</v>
+        <v>23908500</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.15%→2.24%</t>
+          <t>2.14%→2.23%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2297,11 +2297,11 @@
         <v>3</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>35595000</v>
+        <v>30912000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.23%</t>
+          <t>0.08%→0.20%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2318,7 +2318,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 523억   ·   현금 9억(1.7%)      주말 2026-09-04  vs  주초 2026-08-31      매수 4종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 504억   ·   현금 4억(0.9%)      주말 2026-09-04  vs  주초 2026-08-31      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>
@@ -2414,7 +2414,7 @@
         <v>19</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>120843800</v>
+        <v>121867900</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>-234</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-512202600</v>
+        <v>-516543300</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>12</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>539496000</v>
+        <v>544068000</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>-12</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-652068000</v>
+        <v>-657594000</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>9</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>198700200</v>
+        <v>200384100</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>100182000</v>
+        <v>101031000</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_weekly_20260904.xlsx
+++ b/reports/pdf_weekly_20260904.xlsx
@@ -1409,23 +1409,23 @@
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>로보티즈  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-2180178000</v>
+        <v>-1206305100</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>4.59%→4.13%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>119→106</t>
         </is>
       </c>
     </row>
@@ -1437,23 +1437,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>로보티즈  (편출)</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-1206305100</v>
+        <v>-2180178000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>4.59%→4.13%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>119→106</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260904.xlsx
+++ b/reports/pdf_weekly_20260904.xlsx
@@ -1409,23 +1409,23 @@
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>로보티즈  (편출)</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1206305100</v>
+        <v>-2180178000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>4.59%→4.13%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>119→106</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -1437,23 +1437,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>로보티즈  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-2180178000</v>
+        <v>-1206305100</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>4.59%→4.13%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>119→106</t>
         </is>
       </c>
     </row>
